--- a/academias/Biología - Estadisticos 20231.xlsx
+++ b/academias/Biología - Estadisticos 20231.xlsx
@@ -522,10 +522,10 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -554,10 +554,10 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -659,19 +659,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>91.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="H6" s="1">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6" s="2">
         <v>7.7</v>
@@ -761,19 +761,19 @@
         <v>16</v>
       </c>
       <c r="D9">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E9">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F9">
         <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>92.8</v>
+        <v>92.7</v>
       </c>
       <c r="H9" s="1">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="I9" s="2">
         <v>8.300000000000001</v>
@@ -1115,28 +1115,28 @@
         <v>18</v>
       </c>
       <c r="D2">
+        <v>38</v>
+      </c>
+      <c r="E2">
         <v>37</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
       <c r="F2">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>2.6</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1147,28 +1147,28 @@
         <v>16</v>
       </c>
       <c r="D3">
+        <v>38</v>
+      </c>
+      <c r="E3">
         <v>37</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
       <c r="F3">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>2.6</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1185,25 +1185,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>2.8</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1220,25 +1220,25 @@
         <v>23</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>4.3</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1252,28 +1252,28 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>11.1</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1290,25 +1290,25 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>7.7</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1325,25 +1325,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1354,28 +1354,28 @@
         <v>16</v>
       </c>
       <c r="D9">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="F9">
-        <v>152</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J9">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1564,25 +1564,25 @@
         <v>24</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F15">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J15">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1596,25 +1596,25 @@
         <v>24</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J16">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:11">
@@ -1625,25 +1625,25 @@
         <v>359</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="F17">
-        <v>359</v>
+        <v>155</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>56.8</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>43.2</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="J17">
-        <v>359</v>
+        <v>146</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>40.7</v>
       </c>
     </row>
   </sheetData>
@@ -1708,22 +1708,22 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>37</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1740,22 +1740,22 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>37</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1778,19 +1778,19 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>94.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="H4" s="1">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="I4" s="2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1813,19 +1813,19 @@
         <v>23</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>82.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="H5" s="1">
-        <v>17.4</v>
+        <v>4.3</v>
       </c>
       <c r="I5" s="2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1845,22 +1845,22 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>91.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>8.1</v>
+        <v>11.1</v>
       </c>
       <c r="I6" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1947,22 +1947,22 @@
         <v>16</v>
       </c>
       <c r="D9">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E9">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>92.8</v>
+        <v>94.7</v>
       </c>
       <c r="H9" s="1">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="I9" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2218,19 +2218,19 @@
         <v>359</v>
       </c>
       <c r="E17">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F17">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G17" s="1">
-        <v>91.40000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="I17" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J17">
         <v>0</v>

--- a/academias/Biología - Estadisticos 20231.xlsx
+++ b/academias/Biología - Estadisticos 20231.xlsx
@@ -1462,25 +1462,25 @@
         <v>42</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F12">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>2.4</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1529,25 +1529,25 @@
         <v>146</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F14">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J14">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1625,25 +1625,25 @@
         <v>359</v>
       </c>
       <c r="E17">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="F17">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="G17" s="1">
-        <v>56.8</v>
+        <v>68.2</v>
       </c>
       <c r="H17" s="1">
-        <v>43.2</v>
+        <v>31.8</v>
       </c>
       <c r="I17" s="2">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J17">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="K17" s="1">
-        <v>40.7</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2055,19 +2055,19 @@
         <v>42</v>
       </c>
       <c r="E12">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>92.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
       <c r="I12" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2122,16 +2122,16 @@
         <v>146</v>
       </c>
       <c r="E14">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G14" s="1">
-        <v>86.3</v>
+        <v>87.7</v>
       </c>
       <c r="H14" s="1">
-        <v>13.7</v>
+        <v>12.3</v>
       </c>
       <c r="I14" s="2">
         <v>8.199999999999999</v>
@@ -2218,16 +2218,16 @@
         <v>359</v>
       </c>
       <c r="E17">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F17">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G17" s="1">
-        <v>91.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="H17" s="1">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="I17" s="2">
         <v>8.5</v>

--- a/academias/Biología - Estadisticos 20231.xlsx
+++ b/academias/Biología - Estadisticos 20231.xlsx
@@ -1392,25 +1392,25 @@
         <v>30</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1427,25 +1427,25 @@
         <v>42</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F11">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>2.4</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J11">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1497,25 +1497,25 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1529,25 +1529,25 @@
         <v>146</v>
       </c>
       <c r="E14">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="F14">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1">
-        <v>28.1</v>
+        <v>89</v>
       </c>
       <c r="H14" s="1">
-        <v>71.90000000000001</v>
+        <v>11</v>
       </c>
       <c r="I14" s="2">
-        <v>2.2</v>
+        <v>8.5</v>
       </c>
       <c r="J14">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>71.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1625,25 +1625,25 @@
         <v>359</v>
       </c>
       <c r="E17">
-        <v>245</v>
+        <v>334</v>
       </c>
       <c r="F17">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="G17" s="1">
-        <v>68.2</v>
+        <v>93</v>
       </c>
       <c r="H17" s="1">
-        <v>31.8</v>
+        <v>7</v>
       </c>
       <c r="I17" s="2">
-        <v>6.2</v>
+        <v>8.5</v>
       </c>
       <c r="J17">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1997,7 @@
         <v>20</v>
       </c>
       <c r="I10" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2032,7 +2032,7 @@
         <v>2.4</v>
       </c>
       <c r="I11" s="2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2090,19 +2090,19 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>68.8</v>
+        <v>75</v>
       </c>
       <c r="H13" s="1">
-        <v>31.2</v>
+        <v>25</v>
       </c>
       <c r="I13" s="2">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2122,19 +2122,19 @@
         <v>146</v>
       </c>
       <c r="E14">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1">
-        <v>87.7</v>
+        <v>89</v>
       </c>
       <c r="H14" s="1">
-        <v>12.3</v>
+        <v>11</v>
       </c>
       <c r="I14" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2218,19 +2218,19 @@
         <v>359</v>
       </c>
       <c r="E17">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F17">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G17" s="1">
-        <v>92.5</v>
+        <v>93</v>
       </c>
       <c r="H17" s="1">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="I17" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J17">
         <v>0</v>

--- a/academias/Biología - Estadisticos 20231.xlsx
+++ b/academias/Biología - Estadisticos 20231.xlsx
@@ -1404,7 +1404,7 @@
         <v>20</v>
       </c>
       <c r="I10" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1497,19 +1497,19 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>75</v>
+        <v>81.2</v>
       </c>
       <c r="H13" s="1">
-        <v>25</v>
+        <v>18.8</v>
       </c>
       <c r="I13" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1529,19 +1529,19 @@
         <v>146</v>
       </c>
       <c r="E14">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1">
-        <v>89</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="I14" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1625,16 +1625,16 @@
         <v>359</v>
       </c>
       <c r="E17">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G17" s="1">
-        <v>93</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="I17" s="2">
         <v>8.5</v>
@@ -1997,7 +1997,7 @@
         <v>20</v>
       </c>
       <c r="I10" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2090,19 +2090,19 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>75</v>
+        <v>81.2</v>
       </c>
       <c r="H13" s="1">
-        <v>25</v>
+        <v>18.8</v>
       </c>
       <c r="I13" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2122,19 +2122,19 @@
         <v>146</v>
       </c>
       <c r="E14">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1">
-        <v>89</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="I14" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2218,16 +2218,16 @@
         <v>359</v>
       </c>
       <c r="E17">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G17" s="1">
-        <v>93</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="I17" s="2">
         <v>8.6</v>

--- a/academias/Biología - Estadisticos 20231.xlsx
+++ b/academias/Biología - Estadisticos 20231.xlsx
@@ -1711,19 +1711,19 @@
         <v>38</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>97.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>2.6</v>
+        <v>7.9</v>
       </c>
       <c r="I2" s="2">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1743,19 +1743,19 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>97.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>2.6</v>
+        <v>7.9</v>
       </c>
       <c r="I3" s="2">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1813,19 +1813,19 @@
         <v>23</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1848,16 +1848,16 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>88.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="H6" s="1">
-        <v>11.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6" s="2">
         <v>7.8</v>
@@ -1883,16 +1883,16 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="H7" s="1">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="I7" s="2">
         <v>9.199999999999999</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1950,19 +1950,19 @@
         <v>151</v>
       </c>
       <c r="E9">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>94.7</v>
+        <v>96.7</v>
       </c>
       <c r="H9" s="1">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="I9" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1985,19 +1985,19 @@
         <v>30</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>80</v>
+        <v>93.3</v>
       </c>
       <c r="H10" s="1">
-        <v>20</v>
+        <v>6.7</v>
       </c>
       <c r="I10" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2020,19 +2020,19 @@
         <v>42</v>
       </c>
       <c r="E11">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2055,19 +2055,19 @@
         <v>42</v>
       </c>
       <c r="E12">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="H12" s="1">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="I12" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2090,19 +2090,19 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>81.2</v>
+        <v>87.5</v>
       </c>
       <c r="H13" s="1">
-        <v>18.8</v>
+        <v>12.5</v>
       </c>
       <c r="I13" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2122,16 +2122,16 @@
         <v>146</v>
       </c>
       <c r="E14">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F14">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
-        <v>90.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="H14" s="1">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="I14" s="2">
         <v>8.6</v>
@@ -2218,19 +2218,19 @@
         <v>359</v>
       </c>
       <c r="E17">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="F17">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G17" s="1">
-        <v>93.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="H17" s="1">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="I17" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J17">
         <v>0</v>

--- a/academias/Biología - Estadisticos 20231.xlsx
+++ b/academias/Biología - Estadisticos 20231.xlsx
@@ -1723,7 +1723,7 @@
         <v>7.9</v>
       </c>
       <c r="I2" s="2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1755,7 +1755,7 @@
         <v>7.9</v>
       </c>
       <c r="I3" s="2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>2.8</v>
       </c>
       <c r="I4" s="2">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1895,7 +1895,7 @@
         <v>3.8</v>
       </c>
       <c r="I7" s="2">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1962,7 +1962,7 @@
         <v>3.3</v>
       </c>
       <c r="I9" s="2">
-        <v>8.5</v>
+        <v>9.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1997,7 +1997,7 @@
         <v>6.7</v>
       </c>
       <c r="I10" s="2">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2032,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2067,7 +2067,7 @@
         <v>4.8</v>
       </c>
       <c r="I12" s="2">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>12.5</v>
       </c>
       <c r="I13" s="2">
-        <v>7.7</v>
+        <v>9.4</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2134,7 +2134,7 @@
         <v>5.5</v>
       </c>
       <c r="I14" s="2">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2201,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>4.5</v>
       </c>
       <c r="I17" s="2">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>

--- a/academias/Biología - Estadisticos 20231.xlsx
+++ b/academias/Biología - Estadisticos 20231.xlsx
@@ -1723,7 +1723,7 @@
         <v>7.9</v>
       </c>
       <c r="I2" s="2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1755,7 +1755,7 @@
         <v>7.9</v>
       </c>
       <c r="I3" s="2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>2.8</v>
       </c>
       <c r="I4" s="2">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1895,7 +1895,7 @@
         <v>3.8</v>
       </c>
       <c r="I7" s="2">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1962,7 +1962,7 @@
         <v>3.3</v>
       </c>
       <c r="I9" s="2">
-        <v>9.9</v>
+        <v>8.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1997,7 +1997,7 @@
         <v>6.7</v>
       </c>
       <c r="I10" s="2">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2032,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2067,7 +2067,7 @@
         <v>4.8</v>
       </c>
       <c r="I12" s="2">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>12.5</v>
       </c>
       <c r="I13" s="2">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2134,7 +2134,7 @@
         <v>5.5</v>
       </c>
       <c r="I14" s="2">
-        <v>9.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2201,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>4.5</v>
       </c>
       <c r="I17" s="2">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J17">
         <v>0</v>
